--- a/outputs/M6a_tourism_robustness_from_M2_regression_detail.xlsx
+++ b/outputs/M6a_tourism_robustness_from_M2_regression_detail.xlsx
@@ -40,22 +40,22 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>inflation_gdp_deflator_pct</t>
+  </si>
+  <si>
+    <t>trade_pct_gdp</t>
+  </si>
+  <si>
+    <t>ln_gdppc</t>
+  </si>
+  <si>
+    <t>xr_dep_pct</t>
+  </si>
+  <si>
     <t>broad_money_pct_gdp</t>
   </si>
   <si>
     <t>deposit_interest_rate_pct</t>
-  </si>
-  <si>
-    <t>inflation_gdp_deflator_pct</t>
-  </si>
-  <si>
-    <t>trade_pct_gdp</t>
-  </si>
-  <si>
-    <t>ln_gdppc</t>
-  </si>
-  <si>
-    <t>xr_dep_pct</t>
   </si>
   <si>
     <t>ln_tourism_arrivals</t>
@@ -450,19 +450,19 @@
         <v>34.95683525973291</v>
       </c>
       <c r="C2">
-        <v>30.56783713090304</v>
+        <v>30.56783713093058</v>
       </c>
       <c r="D2">
-        <v>1.143582226967336</v>
+        <v>1.143582226966305</v>
       </c>
       <c r="E2">
-        <v>0.2567490035966067</v>
+        <v>0.2567490035970317</v>
       </c>
       <c r="F2">
-        <v>-26.02433127430688</v>
+        <v>-26.02433127436183</v>
       </c>
       <c r="G2">
-        <v>95.93800179377268</v>
+        <v>95.93800179382765</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.08989872487677339</v>
+        <v>0.03020750277910004</v>
       </c>
       <c r="C3">
-        <v>0.08539527515029349</v>
+        <v>0.08480889638918757</v>
       </c>
       <c r="D3">
-        <v>1.052736521061077</v>
+        <v>0.3561831843734644</v>
       </c>
       <c r="E3">
-        <v>0.2961344969637163</v>
+        <v>0.7227901696539991</v>
       </c>
       <c r="F3">
-        <v>-0.08046018775612562</v>
+        <v>-0.1389816162328144</v>
       </c>
       <c r="G3">
-        <v>0.2602576375096724</v>
+        <v>0.1993966217910145</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.2075566583208269</v>
+        <v>-0.04014789116696052</v>
       </c>
       <c r="C4">
-        <v>0.3158598315591145</v>
+        <v>0.02510869603318551</v>
       </c>
       <c r="D4">
-        <v>-0.6571163458686954</v>
+        <v>-1.59896360662848</v>
       </c>
       <c r="E4">
-        <v>0.5132920621447981</v>
+        <v>0.1143981760851753</v>
       </c>
       <c r="F4">
-        <v>-0.8376797811062267</v>
+        <v>-0.09023836919768524</v>
       </c>
       <c r="G4">
-        <v>0.4225664644645728</v>
+        <v>0.009942586863764202</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.03020750277910004</v>
+        <v>-1.635441979545695</v>
       </c>
       <c r="C5">
-        <v>0.08480889638917091</v>
+        <v>2.48535522811965</v>
       </c>
       <c r="D5">
-        <v>0.3561831843735344</v>
+        <v>-0.6580314801852389</v>
       </c>
       <c r="E5">
-        <v>0.7227901696539472</v>
+        <v>0.5127074166167505</v>
       </c>
       <c r="F5">
-        <v>-0.1389816162327812</v>
+        <v>-6.593589996795792</v>
       </c>
       <c r="G5">
-        <v>0.1993966217909813</v>
+        <v>3.322706037704402</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-0.04014789116696052</v>
+        <v>0.07237737367769333</v>
       </c>
       <c r="C6">
-        <v>0.0251086960331829</v>
+        <v>0.08190324936875688</v>
       </c>
       <c r="D6">
-        <v>-1.598963606628647</v>
+        <v>0.8836935559397069</v>
       </c>
       <c r="E6">
-        <v>0.1143981760851382</v>
+        <v>0.3799303934142384</v>
       </c>
       <c r="F6">
-        <v>-0.09023836919768002</v>
+        <v>-0.09101513813289296</v>
       </c>
       <c r="G6">
-        <v>0.009942586863758991</v>
+        <v>0.2357698854882796</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>-1.635441979545695</v>
+        <v>0.08989872487677339</v>
       </c>
       <c r="C7">
-        <v>2.48535522811492</v>
+        <v>0.08539527515028497</v>
       </c>
       <c r="D7">
-        <v>-0.658031480186491</v>
+        <v>1.052736521061182</v>
       </c>
       <c r="E7">
-        <v>0.5127074166159509</v>
+        <v>0.2961344969636686</v>
       </c>
       <c r="F7">
-        <v>-6.593589996786358</v>
+        <v>-0.08046018775610861</v>
       </c>
       <c r="G7">
-        <v>3.322706037694967</v>
+        <v>0.2602576375096554</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.07237737367769333</v>
+        <v>-0.2075566583208269</v>
       </c>
       <c r="C8">
-        <v>0.08190324936875</v>
+        <v>0.315859831559161</v>
       </c>
       <c r="D8">
-        <v>0.8836935559397812</v>
+        <v>-0.6571163458685985</v>
       </c>
       <c r="E8">
-        <v>0.3799303934141987</v>
+        <v>0.5132920621448602</v>
       </c>
       <c r="F8">
-        <v>-0.09101513813287922</v>
+        <v>-0.8376797811063196</v>
       </c>
       <c r="G8">
-        <v>0.2357698854882659</v>
+        <v>0.4225664644646657</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -611,19 +611,19 @@
         <v>-1.224767122010225</v>
       </c>
       <c r="C9">
-        <v>1.223349010648598</v>
+        <v>1.223349010647979</v>
       </c>
       <c r="D9">
-        <v>-1.001159204241213</v>
+        <v>-1.001159204241719</v>
       </c>
       <c r="E9">
-        <v>0.3202479700168341</v>
+        <v>0.320247970016591</v>
       </c>
       <c r="F9">
-        <v>-3.66528162187962</v>
+        <v>-3.665281621878386</v>
       </c>
       <c r="G9">
-        <v>1.215747377859171</v>
+        <v>1.215747377857936</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/M6a_tourism_robustness_from_M2_regression_detail.xlsx
+++ b/outputs/M6a_tourism_robustness_from_M2_regression_detail.xlsx
@@ -52,7 +52,7 @@
     <t>xr_dep_pct</t>
   </si>
   <si>
-    <t>broad_money_pct_gdp</t>
+    <t>broad_money_growth_pct</t>
   </si>
   <si>
     <t>deposit_interest_rate_pct</t>
@@ -447,22 +447,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>34.95683525973291</v>
+        <v>-8.752981343301439</v>
       </c>
       <c r="C2">
-        <v>30.56783713093058</v>
+        <v>20.1742013127759</v>
       </c>
       <c r="D2">
-        <v>1.143582226966305</v>
+        <v>-0.4338700307188051</v>
       </c>
       <c r="E2">
-        <v>0.2567490035970317</v>
+        <v>0.6652100480636929</v>
       </c>
       <c r="F2">
-        <v>-26.02433127436183</v>
+        <v>-48.72171275024192</v>
       </c>
       <c r="G2">
-        <v>95.93800179382765</v>
+        <v>31.21575006363904</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.03020750277910004</v>
+        <v>0.001164540825774268</v>
       </c>
       <c r="C3">
-        <v>0.08480889638918757</v>
+        <v>0.0446600302723331</v>
       </c>
       <c r="D3">
-        <v>0.3561831843734644</v>
+        <v>0.02607568375285454</v>
       </c>
       <c r="E3">
-        <v>0.7227901696539991</v>
+        <v>0.9792429657555688</v>
       </c>
       <c r="F3">
-        <v>-0.1389816162328144</v>
+        <v>-0.08731503399884623</v>
       </c>
       <c r="G3">
-        <v>0.1993966217910145</v>
+        <v>0.08964411565039478</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.04014789116696052</v>
+        <v>-0.01203942465676238</v>
       </c>
       <c r="C4">
-        <v>0.02510869603318551</v>
+        <v>0.01953194416782793</v>
       </c>
       <c r="D4">
-        <v>-1.59896360662848</v>
+        <v>-0.616396634831321</v>
       </c>
       <c r="E4">
-        <v>0.1143981760851753</v>
+        <v>0.5388725651014232</v>
       </c>
       <c r="F4">
-        <v>-0.09023836919768524</v>
+        <v>-0.05073572882246395</v>
       </c>
       <c r="G4">
-        <v>0.009942586863764202</v>
+        <v>0.02665687950893919</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-1.635441979545695</v>
+        <v>0.888907744347213</v>
       </c>
       <c r="C5">
-        <v>2.48535522811965</v>
+        <v>0.5749626638203464</v>
       </c>
       <c r="D5">
-        <v>-0.6580314801852389</v>
+        <v>1.546026899278737</v>
       </c>
       <c r="E5">
-        <v>0.5127074166167505</v>
+        <v>0.1248941543133917</v>
       </c>
       <c r="F5">
-        <v>-6.593589996795792</v>
+        <v>-0.2501969925873467</v>
       </c>
       <c r="G5">
-        <v>3.322706037704402</v>
+        <v>2.028012481281773</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.07237737367769333</v>
+        <v>0.05600271352955316</v>
       </c>
       <c r="C6">
-        <v>0.08190324936875688</v>
+        <v>0.04254306903085246</v>
       </c>
       <c r="D6">
-        <v>0.8836935559397069</v>
+        <v>1.31637690475362</v>
       </c>
       <c r="E6">
-        <v>0.3799303934142384</v>
+        <v>0.1907114271060777</v>
       </c>
       <c r="F6">
-        <v>-0.09101513813289296</v>
+        <v>-0.02828277926188867</v>
       </c>
       <c r="G6">
-        <v>0.2357698854882796</v>
+        <v>0.140288206320995</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.08989872487677339</v>
+        <v>0.04215732573154449</v>
       </c>
       <c r="C7">
-        <v>0.08539527515028497</v>
+        <v>0.03855735166601556</v>
       </c>
       <c r="D7">
-        <v>1.052736521061182</v>
+        <v>1.09336673578393</v>
       </c>
       <c r="E7">
-        <v>0.2961344969636686</v>
+        <v>0.2765581689243082</v>
       </c>
       <c r="F7">
-        <v>-0.08046018775610861</v>
+        <v>-0.03423174209866427</v>
       </c>
       <c r="G7">
-        <v>0.2602576375096554</v>
+        <v>0.1185463935617533</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-0.2075566583208269</v>
+        <v>0.08826342120953533</v>
       </c>
       <c r="C8">
-        <v>0.315859831559161</v>
+        <v>0.1217049060953327</v>
       </c>
       <c r="D8">
-        <v>-0.6571163458685985</v>
+        <v>0.7252248413091719</v>
       </c>
       <c r="E8">
-        <v>0.5132920621448602</v>
+        <v>0.4698132864606779</v>
       </c>
       <c r="F8">
-        <v>-0.8376797811063196</v>
+        <v>-0.1528559483860655</v>
       </c>
       <c r="G8">
-        <v>0.4225664644646657</v>
+        <v>0.3293827908051361</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -608,22 +608,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>-1.224767122010225</v>
+        <v>-0.5259768022160302</v>
       </c>
       <c r="C9">
-        <v>1.223349010647979</v>
+        <v>0.6588279820752174</v>
       </c>
       <c r="D9">
-        <v>-1.001159204241719</v>
+        <v>-0.7983522505514651</v>
       </c>
       <c r="E9">
-        <v>0.320247970016591</v>
+        <v>0.426340773497448</v>
       </c>
       <c r="F9">
-        <v>-3.665281621878386</v>
+        <v>-1.831233860509839</v>
       </c>
       <c r="G9">
-        <v>1.215747377857936</v>
+        <v>0.7792802560777784</v>
       </c>
     </row>
   </sheetData>
